--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="89">
   <si>
     <t>Result</t>
   </si>
@@ -271,6 +271,39 @@
   </si>
   <si>
     <t>Thu Jun 04 18:02:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:08:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:11:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:11:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:12:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:13:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:15:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:16:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -899,7 +932,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>28</v>
@@ -937,7 +970,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>33</v>
@@ -975,7 +1008,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>44</v>
@@ -1016,7 +1049,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>45</v>
@@ -1057,7 +1090,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
@@ -1122,7 +1155,7 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>51</v>
@@ -1334,7 +1367,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>27</v>
@@ -1378,7 +1411,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1449,7 +1482,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>31</v>
@@ -1490,7 +1523,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -1532,7 +1565,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>46</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="105">
   <si>
     <t>Result</t>
   </si>
@@ -304,6 +304,54 @@
   </si>
   <si>
     <t>Thu Jun 18 02:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:56:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:59:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:00:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:02:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:03:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:03:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:05:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:06:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:06:49 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -932,7 +980,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>28</v>
@@ -970,7 +1018,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>33</v>
@@ -1008,7 +1056,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>44</v>
@@ -1049,7 +1097,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>45</v>
@@ -1090,7 +1138,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
@@ -1155,7 +1203,7 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>51</v>
@@ -1367,7 +1415,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>27</v>
@@ -1411,7 +1459,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1482,7 +1530,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>31</v>
@@ -1523,7 +1571,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -1565,7 +1613,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>46</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="127">
   <si>
     <t>Result</t>
   </si>
@@ -352,6 +352,72 @@
   </si>
   <si>
     <t>Mon Jun 29 14:06:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:37:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:40:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:41:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:42:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:44:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:01:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:02:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:04:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:06:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:07:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:08:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:09:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:10:15 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -857,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
@@ -976,11 +1042,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
-        <v>89</v>
+      <c r="B2" t="s" s="1">
+        <v>116</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>28</v>
@@ -1014,11 +1080,11 @@
       </c>
     </row>
     <row ht="37.5" r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>90</v>
+      <c r="B3" t="s" s="1">
+        <v>117</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>33</v>
@@ -1052,11 +1118,11 @@
       </c>
     </row>
     <row ht="62.5" r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
+      <c r="B4" t="s" s="1">
+        <v>118</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>44</v>
@@ -1093,11 +1159,11 @@
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B5" t="s">
-        <v>92</v>
+      <c r="B5" t="s" s="1">
+        <v>119</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>45</v>
@@ -1134,11 +1200,11 @@
       </c>
     </row>
     <row ht="37.5" r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>93</v>
+      <c r="B6" t="s" s="1">
+        <v>120</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
@@ -1199,11 +1265,11 @@
       </c>
     </row>
     <row ht="37.5" r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>94</v>
+      <c r="B7" t="s" s="1">
+        <v>121</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>51</v>
@@ -1279,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -1411,11 +1477,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
-        <v>100</v>
+      <c r="B2" t="s" s="6">
+        <v>122</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>27</v>
@@ -1455,11 +1521,11 @@
       </c>
     </row>
     <row ht="37.5" r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>101</v>
+      <c r="B3" t="s" s="6">
+        <v>123</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1526,11 +1592,11 @@
       </c>
     </row>
     <row ht="37.5" r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>102</v>
+      <c r="B4" t="s" s="6">
+        <v>124</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>31</v>
@@ -1567,11 +1633,11 @@
       </c>
     </row>
     <row customHeight="1" ht="42" r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B5" t="s">
-        <v>103</v>
+      <c r="B5" t="s" s="6">
+        <v>125</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -1609,11 +1675,11 @@
       </c>
     </row>
     <row ht="50" r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>104</v>
+      <c r="B6" t="s" s="6">
+        <v>126</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>46</v>
